--- a/data/export/2026-10-12-operations.xlsx
+++ b/data/export/2026-10-12-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1583,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2506,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2519,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2529,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2567,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2586,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2622,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,7 +2650,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2683,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,35 +2738,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2799,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2970,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3031,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3050,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3086,3603 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-operations.xlsx
+++ b/data/export/2026-10-12-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1686,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1784,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1791,7 +1823,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1802,7 +1834,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1900,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1950,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2070,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2186,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2252,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2302,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2417,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2435,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2488,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2502,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2532,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2603,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2622,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2647,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2723,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2742,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2767,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2843,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2862,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2898,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2959,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2978,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3003,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3079,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3098,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3123,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3199,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3218,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,46 +3243,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3319,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3338,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,7 +3363,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3318,35 +3374,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3435,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3454,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,7 +3479,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3434,7 +3490,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3503,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,7 +3513,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3495,12 +3551,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3570,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3539,7 +3595,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3550,7 +3606,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3619,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3573,7 +3629,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3611,12 +3667,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3655,7 +3711,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3666,7 +3722,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3735,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3806,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3816,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3836,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3859,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3869,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3815,40 +3879,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3930,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3872,17 +3940,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3892,13 +3960,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3983,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +3993,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3931,12 +4003,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4031,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4044,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4102,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4115,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4163,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4182,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4218,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4231,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4153,7 +4241,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4191,12 +4279,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4298,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4334,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4347,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4357,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4395,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4414,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4450,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4463,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4385,7 +4473,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4423,12 +4511,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4530,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4566,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4579,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4501,7 +4589,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4539,12 +4627,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4646,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4682,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4695,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4617,7 +4705,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4655,12 +4743,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4762,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4798,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4811,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4859,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4878,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4914,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +4975,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +4994,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5019,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5030,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5091,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5110,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5146,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5207,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5226,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5262,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5323,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5342,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5378,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5439,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5458,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5494,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5555,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5574,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5610,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5671,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5690,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5726,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5787,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5806,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5842,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5903,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5922,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5958,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6019,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6038,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6074,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6135,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6154,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6190,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6251,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6270,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6306,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6367,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6386,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6422,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6483,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6502,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6538,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6511,12 +6599,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6618,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6566,35 +6654,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6627,12 +6715,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6734,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6682,7 +6770,2967 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-operations.xlsx
+++ b/data/export/2026-10-12-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD78"/>
+  <dimension ref="A1:AD99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1521,24 +1521,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1635,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,17 +1696,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,13 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1751,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1784,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1808,17 +1820,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1828,13 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1900,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1924,33 +1944,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1983,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2016,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2040,37 +2068,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2103,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2136,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2160,33 +2192,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2219,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2252,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2276,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2335,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2368,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2392,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2608,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2782,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2964,7 +3012,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3018,7 +3066,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3132,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3138,7 +3186,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3252,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3253,12 +3301,12 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3372,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3368,13 +3416,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3492,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3484,41 +3536,45 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3551,12 +3607,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3570,7 +3626,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3600,41 +3656,45 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3667,12 +3727,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3686,7 +3746,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3711,88 +3771,88 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3806,7 +3866,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3816,107 +3876,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3930,7 +3986,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3940,75 +3996,75 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4031,12 +4087,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4044,29 +4100,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq32（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4091,18 +4131,22 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4115,60 +4159,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4182,7 +4230,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4192,33 +4240,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4231,52 +4283,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4284,7 +4340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4298,7 +4354,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4308,33 +4364,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4407,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4357,7 +4417,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4367,40 +4427,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4414,7 +4478,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4424,33 +4488,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4531,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4473,7 +4541,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4511,12 +4579,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4530,7 +4598,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4555,7 +4623,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4579,7 +4647,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4589,7 +4657,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4599,12 +4667,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4627,12 +4695,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4640,13 +4708,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4671,7 +4755,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4695,60 +4779,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4762,7 +4850,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4772,33 +4860,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4903,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4821,7 +4913,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4859,12 +4951,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4878,7 +4970,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4903,7 +4995,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4927,7 +5019,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4937,7 +5029,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4947,40 +5039,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4994,7 +5090,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5004,33 +5100,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5143,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5053,7 +5153,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5091,12 +5191,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5110,7 +5210,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5159,22 +5259,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5207,12 +5307,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5226,7 +5326,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5275,22 +5375,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5323,12 +5423,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5342,7 +5442,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5391,7 +5491,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5401,7 +5501,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5439,12 +5539,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5458,7 +5558,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5507,7 +5607,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5517,7 +5617,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5555,12 +5655,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5574,7 +5674,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5623,7 +5723,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5633,7 +5733,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5671,12 +5771,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5690,7 +5790,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5739,22 +5839,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5787,12 +5887,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5806,7 +5906,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5855,22 +5955,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5903,12 +6003,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5922,7 +6022,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5971,22 +6071,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6019,12 +6119,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6038,7 +6138,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6087,22 +6187,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6135,12 +6235,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6154,7 +6254,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6203,22 +6303,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6251,12 +6351,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6270,7 +6370,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6319,22 +6419,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6367,12 +6467,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6386,7 +6486,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6435,22 +6535,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6488,7 +6588,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6502,7 +6602,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6551,22 +6651,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6599,12 +6699,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6618,7 +6718,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6667,22 +6767,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6715,12 +6815,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6734,7 +6834,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6759,7 +6859,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6783,22 +6883,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6836,7 +6936,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6850,7 +6950,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6875,7 +6975,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6893,28 +6993,28 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6947,12 +7047,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6966,7 +7066,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6991,7 +7091,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7002,77 +7102,73 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7086,7 +7182,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7096,107 +7192,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7210,7 +7298,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7220,107 +7308,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7334,7 +7414,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7344,17 +7424,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7369,40 +7449,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7435,12 +7515,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7454,7 +7534,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7479,88 +7559,88 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7574,7 +7654,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7584,17 +7664,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7609,82 +7689,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7698,7 +7774,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7708,17 +7784,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7728,45 +7804,41 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7799,12 +7871,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7818,7 +7890,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7843,7 +7915,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7854,35 +7926,35 @@
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7915,12 +7987,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7934,7 +8006,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7959,46 +8031,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8031,12 +8107,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8050,7 +8126,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8075,7 +8151,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8086,35 +8162,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8147,12 +8223,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8166,7 +8242,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8191,18 +8267,22 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8295,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8225,7 +8305,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8263,12 +8343,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8282,7 +8362,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8307,7 +8387,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8331,60 +8411,64 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:32</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8398,7 +8482,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8408,33 +8492,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8535,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8457,7 +8545,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8467,40 +8555,44 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8514,7 +8606,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8524,33 +8616,37 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8659,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8573,7 +8669,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8583,40 +8679,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8630,7 +8730,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8640,33 +8740,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8783,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8689,7 +8793,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8732,7 +8836,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8746,7 +8850,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8771,7 +8875,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8795,7 +8899,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8805,7 +8909,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8815,40 +8919,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8862,7 +8970,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8872,17 +8980,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8892,13 +9000,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8911,60 +9023,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:08</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8978,7 +9094,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8988,33 +9104,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9147,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9037,7 +9157,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9080,7 +9200,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9094,7 +9214,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9124,17 +9244,13 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9147,60 +9263,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9214,7 +9334,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9224,17 +9344,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9249,12 +9369,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9267,60 +9387,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9334,7 +9458,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9344,17 +9468,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9369,12 +9493,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9387,60 +9511,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9454,7 +9582,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9464,17 +9592,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9489,12 +9617,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9507,60 +9635,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9574,7 +9706,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9584,33 +9716,37 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9623,60 +9759,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9690,47 +9830,2547 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X78" s="2" t="inlineStr">
+      <c r="X89" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y78" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z78" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB78" s="2" t="inlineStr">
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="AD78" s="2" t="inlineStr">
-        <is>
-          <t>3/18</t>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-operations.xlsx
+++ b/data/export/2026-10-12-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD99"/>
+  <dimension ref="A1:AD102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2623,32 +2623,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2680,32 +2684,32 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2776,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3012,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3132,7 +3136,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3252,7 +3256,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3372,7 +3376,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3492,7 +3496,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3732,7 +3736,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3852,7 +3856,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3901,7 +3905,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -3972,7 +3976,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4092,7 +4096,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4141,7 +4145,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4153,70 +4157,66 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4240,37 +4240,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4283,24 +4283,24 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4313,24 +4313,24 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4437,19 +4437,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4531,52 +4531,56 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4584,7 +4588,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4598,7 +4602,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4608,17 +4612,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4628,13 +4632,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4647,32 +4655,32 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4700,7 +4708,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4708,29 +4716,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>物理seq32（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4779,7 +4771,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4789,7 +4781,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4799,44 +4791,40 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4844,13 +4832,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4860,17 +4864,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4880,17 +4884,13 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>163.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4903,60 +4903,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4970,7 +4974,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4980,17 +4984,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5000,13 +5004,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5019,64 +5027,60 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5090,7 +5094,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5100,17 +5104,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5120,17 +5124,13 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5143,60 +5143,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5220,33 +5224,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5259,22 +5267,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5307,12 +5315,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5326,7 +5334,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5351,7 +5359,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5375,22 +5383,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5428,7 +5436,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5467,7 +5475,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5491,7 +5499,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5501,7 +5509,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5539,12 +5547,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5558,7 +5566,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5607,32 +5615,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5655,12 +5663,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5668,13 +5676,21 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5723,22 +5739,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5776,7 +5792,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5839,7 +5855,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5849,7 +5865,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5887,12 +5903,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5906,7 +5922,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5955,32 +5971,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq42，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -6003,12 +6019,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6016,13 +6032,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq39（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6071,22 +6103,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6119,12 +6151,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6187,22 +6219,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6235,12 +6267,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6254,7 +6286,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6303,22 +6335,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6351,12 +6383,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6370,7 +6402,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6419,22 +6451,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6472,7 +6504,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6486,7 +6518,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6535,22 +6567,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6583,12 +6615,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6602,7 +6634,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6651,22 +6683,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6699,12 +6731,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6718,7 +6750,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6767,22 +6799,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6820,7 +6852,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6834,7 +6866,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6883,22 +6915,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6931,12 +6963,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6950,7 +6982,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6999,22 +7031,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7052,7 +7084,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7066,7 +7098,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7115,22 +7147,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7168,7 +7200,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7182,7 +7214,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7231,22 +7263,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7279,12 +7311,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7298,7 +7330,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7347,22 +7379,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7395,12 +7427,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7414,7 +7446,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7439,22 +7471,18 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>162.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7467,22 +7495,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7520,7 +7548,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7534,7 +7562,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7569,12 +7597,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7615,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7597,7 +7625,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7640,7 +7668,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7654,7 +7682,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7689,12 +7717,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -7707,22 +7735,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7760,7 +7788,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7774,7 +7802,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7804,13 +7832,17 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7855,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7833,7 +7865,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7876,7 +7908,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7890,7 +7922,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7939,22 +7971,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7987,12 +8019,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8006,7 +8038,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8036,17 +8068,13 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>163.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8059,22 +8087,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8107,12 +8135,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8156,13 +8184,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -8175,22 +8207,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8223,12 +8255,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8242,7 +8274,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8272,45 +8304,41 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>158.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8343,12 +8371,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8362,7 +8390,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8392,83 +8420,83 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8482,7 +8510,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8492,107 +8520,99 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8606,7 +8626,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8616,17 +8636,17 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8636,17 +8656,13 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8659,64 +8675,60 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8740,17 +8752,17 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8765,12 +8777,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8795,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8793,7 +8805,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8803,40 +8815,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8850,7 +8866,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8860,33 +8876,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8899,24 +8919,24 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8929,12 +8949,12 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -8951,12 +8971,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8970,7 +8990,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9005,12 +9025,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9043,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9033,7 +9053,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9053,12 +9073,12 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
@@ -9080,7 +9100,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9094,7 +9114,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9129,12 +9149,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9167,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9157,7 +9177,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9195,12 +9215,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9214,7 +9234,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9263,24 +9283,24 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9293,34 +9313,34 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9334,7 +9354,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9369,12 +9389,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9407,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9397,7 +9417,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9417,7 +9437,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -9429,22 +9449,22 @@
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9458,7 +9478,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9498,7 +9518,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9531,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9521,7 +9541,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9531,44 +9551,40 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9582,7 +9598,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9592,17 +9608,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9612,17 +9628,13 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9647,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9645,7 +9657,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9665,12 +9677,12 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
@@ -9687,12 +9699,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9706,7 +9718,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9741,12 +9753,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9771,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9769,7 +9781,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9789,34 +9801,34 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9865,12 +9877,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9895,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9893,7 +9905,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9913,34 +9925,34 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9954,7 +9966,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9979,22 +9991,22 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10007,24 +10019,24 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10037,34 +10049,34 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10078,7 +10090,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10113,12 +10125,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10131,60 +10143,64 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10198,7 +10214,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10208,17 +10224,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10228,13 +10244,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10247,55 +10267,59 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10314,7 +10338,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10324,33 +10348,37 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10363,60 +10391,64 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>08:08</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10430,7 +10462,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10440,33 +10472,37 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10515,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10489,7 +10525,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10527,12 +10563,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10546,7 +10582,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10576,17 +10612,13 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10631,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10609,7 +10641,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10619,32 +10651,36 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10652,7 +10688,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10666,7 +10702,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10676,22 +10712,22 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10701,12 +10737,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10755,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10729,7 +10765,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10767,12 +10803,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10786,7 +10822,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10811,22 +10847,18 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10839,22 +10871,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10887,12 +10919,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10906,7 +10938,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10941,12 +10973,12 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10991,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -10969,7 +11001,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -11007,12 +11039,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11026,7 +11058,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11051,18 +11083,22 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB88" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11111,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11085,7 +11121,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -11128,7 +11164,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11142,7 +11178,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11177,12 +11213,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11231,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11205,7 +11241,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11243,12 +11279,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11262,7 +11298,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11292,13 +11328,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11351,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -11321,7 +11361,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11359,12 +11399,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11378,7 +11418,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11403,7 +11443,7 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
@@ -11427,7 +11467,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11437,7 +11477,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11475,12 +11515,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11494,7 +11534,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11534,7 +11574,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11587,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11557,7 +11597,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11595,12 +11635,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11614,7 +11654,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11644,17 +11684,13 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>111.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11667,22 +11703,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11715,12 +11751,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11734,7 +11770,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11764,17 +11800,13 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11787,22 +11819,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11835,12 +11867,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11854,7 +11886,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11889,12 +11921,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11939,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11917,7 +11949,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11955,12 +11987,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11974,7 +12006,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -12009,12 +12041,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12059,7 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -12037,7 +12069,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -12075,12 +12107,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12094,7 +12126,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12129,12 +12161,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12179,7 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -12157,7 +12189,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12195,12 +12227,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12214,7 +12246,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12244,13 +12276,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12263,22 +12299,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -12311,12 +12347,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12330,47 +12366,403 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
+      <c r="AB102" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AC102" s="2" t="inlineStr">
         <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="AD99" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-12-operations.xlsx
+++ b/data/export/2026-10-12-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2460,17 +2460,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4184,17 +4184,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4924,17 +4924,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6040,17 +6040,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6412,17 +6412,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7032,17 +7032,17 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8024,17 +8024,17 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8148,17 +8148,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8768,17 +8768,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9632,17 +9632,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10004,17 +10004,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10252,17 +10252,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10996,17 +10996,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11364,17 +11364,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11407,32 +11407,36 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11440,7 +11444,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11464,17 +11468,17 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11484,17 +11488,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11568,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11618,7 +11622,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11651,32 +11655,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11684,7 +11692,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11708,17 +11716,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11728,12 +11736,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11804,7 +11812,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11891,32 +11899,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11924,7 +11936,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11948,17 +11960,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11968,17 +11980,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -12011,32 +12023,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12044,7 +12060,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12068,17 +12084,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12088,17 +12104,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12131,32 +12147,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12164,7 +12184,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12188,17 +12208,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12208,17 +12228,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12304,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12338,7 +12358,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12424,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12448,17 +12468,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12602,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12672,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12696,17 +12716,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13172,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13206,7 +13226,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13346,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13470,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13660,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13694,7 +13714,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13760,7 +13780,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13804,17 +13824,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -14248,7 +14268,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14384,7 +14404,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14438,7 +14458,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14508,7 +14528,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14552,17 +14572,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14772,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14806,7 +14826,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14892,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14996,7 +15016,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15045,12 +15065,12 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -15244,7 +15264,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15422,7 +15442,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15512,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15536,17 +15556,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -15736,7 +15756,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15790,7 +15810,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15934,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -15980,7 +16000,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16024,17 +16044,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -16476,7 +16496,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16530,7 +16550,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16654,7 +16674,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16798,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -16972,7 +16992,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17026,7 +17046,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17112,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17136,17 +17156,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17484,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17518,7 +17538,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17608,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17632,17 +17652,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17708,7 +17728,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17752,17 +17772,17 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17976,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18010,7 +18030,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18100,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18328,7 +18348,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18576,7 +18596,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18630,7 +18650,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -19126,7 +19146,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -19192,7 +19212,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19576,7 +19596,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19824,7 +19844,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19868,17 +19888,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20072,7 +20092,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20126,7 +20146,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -20622,7 +20642,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -20870,7 +20890,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -21192,7 +21212,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21236,17 +21256,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21312,7 +21332,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21432,7 +21452,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21481,12 +21501,12 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21556,7 +21576,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21600,17 +21620,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21700,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21724,17 +21744,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21800,7 +21820,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21924,7 +21944,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22048,7 +22068,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22102,7 +22122,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22172,7 +22192,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22216,17 +22236,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22316,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22350,7 +22370,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22594,7 +22614,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -22664,7 +22684,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22718,7 +22738,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -23036,7 +23056,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23090,7 +23110,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23338,7 +23358,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -23586,7 +23606,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23772,7 +23792,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23869,24 +23889,24 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O190" s="2" t="inlineStr">
@@ -23896,7 +23916,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23945,12 +23965,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23983,32 +24003,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24016,7 +24040,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24040,17 +24064,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24060,17 +24084,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24103,32 +24127,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24136,7 +24164,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24160,17 +24188,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24180,17 +24208,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24284,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24343,32 +24371,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24376,7 +24408,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24400,17 +24432,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24420,17 +24452,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24463,32 +24495,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24496,7 +24532,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24520,17 +24556,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24540,17 +24576,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24583,12 +24619,12 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq53，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24616,18 +24652,34 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
           <t>20:21</t>
         </is>
       </c>
-      <c r="Q196" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V196" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24670,7 +24722,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24736,7 +24788,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24823,32 +24875,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>10:11</t>
@@ -24856,7 +24912,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24880,17 +24936,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -24900,17 +24956,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -24976,7 +25032,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25030,7 +25086,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25152,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25150,7 +25206,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -25216,7 +25272,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25270,7 +25326,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25336,7 +25392,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25390,7 +25446,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25512,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25576,7 +25632,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25620,17 +25676,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25934,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26068,7 +26124,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26122,7 +26178,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26192,7 +26248,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26241,7 +26297,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26370,7 +26426,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26560,7 +26616,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26614,7 +26670,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -26684,7 +26740,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26728,17 +26784,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26918,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27424,7 +27480,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27468,12 +27524,12 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
@@ -27548,7 +27604,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27592,17 +27648,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28100,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28093,7 +28149,7 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28222,7 +28278,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28346,7 +28402,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28470,7 +28526,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28592,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28590,7 +28646,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28840,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28828,17 +28884,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28908,7 +28964,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28962,7 +29018,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29210,7 +29266,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29520,7 +29576,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29564,12 +29620,12 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
@@ -29942,7 +29998,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30008,7 +30064,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30069,7 +30125,7 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30198,7 +30254,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30264,7 +30320,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30320,17 +30376,17 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30702,7 +30758,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31378,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31446,7 +31502,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -31818,7 +31874,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32438,7 +32494,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32508,7 +32564,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32552,17 +32608,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32686,7 +32742,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33054,7 +33110,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33124,7 +33180,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33178,7 +33234,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33488,7 +33544,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33542,7 +33598,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -33856,7 +33912,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33905,7 +33961,7 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
@@ -33980,7 +34036,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34024,12 +34080,12 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34352,7 +34408,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34396,17 +34452,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -34530,7 +34586,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34654,7 +34710,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34724,7 +34780,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34768,17 +34824,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35146,7 +35202,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35340,7 +35396,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35394,7 +35450,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35588,7 +35644,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35642,7 +35698,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35960,7 +36016,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36009,7 +36065,7 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36084,7 +36140,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36128,12 +36184,12 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36510,7 +36566,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36580,7 +36636,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36624,17 +36680,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36758,7 +36814,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36948,7 +37004,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36992,17 +37048,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37250,7 +37306,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37429,12 +37485,12 @@
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O300" s="2" t="inlineStr">
@@ -37444,7 +37500,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37498,7 +37554,7 @@
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37541,24 +37597,24 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -37568,7 +37624,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37617,7 +37673,7 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
@@ -37677,12 +37733,12 @@
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37692,7 +37748,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37746,7 +37802,7 @@
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37779,32 +37835,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37812,7 +37872,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37836,17 +37896,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37856,17 +37916,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37899,32 +37959,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37932,7 +37996,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37956,17 +38020,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37976,12 +38040,12 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
@@ -38019,32 +38083,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -38052,7 +38120,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38076,17 +38144,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38096,17 +38164,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38172,7 +38240,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38226,7 +38294,7 @@
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -38292,7 +38360,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38346,7 +38414,7 @@
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -38412,7 +38480,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38456,12 +38524,12 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
